--- a/pacjenci/ANNA TOKARCZYK.xlsx
+++ b/pacjenci/ANNA TOKARCZYK.xlsx
@@ -798,7 +798,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -806,17 +806,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/ANNA TOKARCZYK.xlsx
+++ b/pacjenci/ANNA TOKARCZYK.xlsx
@@ -413,38 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -452,372 +452,269 @@
           <t>SUVmax</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>03.01.2023</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina- ocena zaawansowania choroby.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 77mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane przedziałów I - V obustronnie i nadobojczykowe obustronnie  wielkości do 35x25mm wg PET, SUV max do 6,2 (największy pakiet IM 83 strona lewa).  Poza tym fzjologiczny metabolizm FDG w obrębie głowy i szyi. Drobny polip lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane:  - podobojczykowe obustronnie, śródpiersiowe obustronnie, pachowe obustronnie, pojedyncze w strukturach mięśniowych ściany KLP wielkości do 21mm wg PET, SUV max do 5,8 - przytchawicze obustronnie, przy łuku aorty, przy tętnicy płucnej lewej, okna aortalno-płucnego wielkości do 23mm wg PET, SUV max do 5,6 - podostrogowe, obu wnęk wielkości do 38mm wg PET, SUV max do 7,6 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zgrubienie opłucnej płuca prawego grzbietowo. Drobne guzki w płacie górnym płuca prawego, w płacie górnym płuca lewego, w segm. 6L średnicy do 6mm.  Brzuch i miednica: Niejednoznaczny obszar pobudzenia metabolicznego przy torebce wątroby na poziomie segmentu 4 wielkości 11mm wg PET, SUV max 3,9- nie da się wykluczyć wychwytu pochodzącego z żebra 7. - celowa kontrola.  Drobny niejednoznaczny obszar pobudzenia metabolicznego wielkości 7mm wg PET, SUV max 3,1 dobocznie od żyły głównej dolnej [Im 181] węzeł chłonny krezkowy?- do oceny w badaniu TK z kontrastem dożylnym.  Obszar miękkotkankowy w miednicy po stronie lewej wielkości 27x25mm, SUV max 5,4 ze zwiększona aktywnością metaboliczną na obwodzie zmiany- zmiana ogniskowa przydatka lewego?- do oceny w USG- TV miednicy i konsultacji ginekologicznej. Zwiększona aktywność metaboliczna w macicy- związana z fazą cyklu?- do kontroli.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym do oceny z całością obrazu klinicznego ew. weryfikacji w trepanobiopsji.  Wartości referencyjne: MBPS SUVmax do 1,8 Prawy płat wątroby SUVmax do 2,6.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - aktywnych metabolicznie węzłow chłonnych na szyi i w KLP - niejednoznacznego obszaru przy torebce wątroby - nie da się wykluczyć wychwytu pochodzącego z żebra - celowa kontrola - niejednoznacznego obszaru w jamie brzusznej - węzeł chłonny krezkowy? - obszaru miękkotkankowego w miednicy po stronie lewej ze zwiększoną aktywnością metaboliczną na obwodzie zmiany- zmiana ogniskowa przydatka lewego?- do oceny w USG - TV i konsultacji ginekologicznej. Pobudzenie metaboliczne w układzie kostnym do oceny z całością obrazu klinicznego ew. weryfikacji w trepanobiopsji. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>7.6</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>23.02.2023</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina- ocena odpowiedzi na leczenie po 2 cyklach BEACOPP.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 57min od podania 18F-FDG. Glikemia: 68mg%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobny polip lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Bardzo drobne guzki w płacie górnym płuca prawego, w płacie górnym płuca lewego,  średnicy do 2-3mm. Węzły chłonne w śródpiersiu średnicy do 17mm.  Węzły chłonne pachowych obustronnie średnicy do 14mm.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym do oceny z całością obrazu klinicznego ew. weryfikacji w trepanobiopsji.  Wartości referencyjne: MBPS SUVmax do 2,5 Prawy płat wątroby SUVmax do 3,6,</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3.6</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>13.07.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina- ocena odpowiedzi na leczenie po 3 cyklach BEACOPP oraz 3 ABVD.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 56min od podania 18F-FDG. Glikemia: 76mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Drobne zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne w śródpiersiu wielkości do 17x15mm.  Węzły chłonne pachowe obustronnie wielkości do 15x11mm [strona prawa].  Brzuch i miednica: Wzmożona aktywność metaboliczna w topografii przydatków obustronnie, SUV max do 5,1 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwiększona ilość płynu w jamie Douglasa.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Wzmożona aktywność metaboliczna w brunatnej tkance tłuszczowej głowy i szyi, klatki piersiowej oraz nadbrzusza, SUV max do 11,6.  Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 2,9.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>11.6</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>04.01.2024</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Stan po 3 cyklach BEACOPP. Ocena odpowiedzi po zakończonym leczeniu.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 60min od podania 18F-FDG. Glikemia: 94mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Wzmożona aktywność metaboliczna w topografii mięśni jarzmowych obustronnie, SUVmax 4,8  [Im fuz 48] - w pierwszej kolejności czynnościowo. Wzmożona aktywność metaboliczna SUVmax do 4,7 w obrębie fałdów głosowych - czynnościowo. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Aktywne i pobudzone metabolicznie dość liczne, przylegające do siebie węzły chłonne w śródpiersiu przednim, zamostkowo, wielkości do 19x16mm, SUV max do 4,6  [Im fuz 109]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Poza powyższymi - węzły chłonne w śródpiersiu wielkości do 15x11mm.  Węzły chłonne międzypiersiowe i pachowe obustronnie wielkości do 15x11mm [strona prawa].  Brzuch i miednica: Wzmożona aktywność metaboliczna w topografii przydatków obustronnie, SUV max do 4,1 - w pierwszej kolejności czynnościowo. Utrzymuje się asymetria aktywności znacznika w nieposzerzonym UKM-ie nerki prawej i w prawym moczowodzie - zaburzenia odpływu moczu? do kontroli w wielofazowym badaniu TK jamy brzusznej i miednicy z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Wzmożona aktywność metaboliczna w brunatnej tkance tłuszczowej głowy i szyi, klatki piersiowej oraz nadbrzusza, SUV max do 14,5 - porównywalnie do poprzedniego badania PET z 13.07.2023r.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 3,2.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych i pobudzonych metabolicznie dość licznych, przylegających do siebie węzłów chłonnch w śródpiersiu przednim, zamostkowo - w porównaniu do poprzedniego badania PET/CT z dnia 13.07.2023r - progresja. Poza tym aktualny obraz badania PET porównywalny do poprzedniego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>14.5</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5 - znacznie zwiększony wychwyt lub nowe zmiany</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Progresja choroby. Klasyfikacja Lugano: Progressive Disease (PD) - progresja choroby. Deauville: 5 - znacznie zwiększony wychwyt lub nowe zmiany.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>02.07.2024</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Stan po 3 cyklach BEACOPP. Badanie kontrolne.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 57min od podania 18F-FDG. Glikemia: 83mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Pobudzenie metaboliczne na tylnej ścianie nosogardła, SUV max 5,3 -do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. Niewielkie przyścienne zgrubienia blony sluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Węzeł chłonny w śródpiersiu przednim, górnym po stronie lewej, wielkości 9mm, SUV max 3,7 [Im. Fuz. 93]. Aktywne metabolicznie przylegające do siebie węzły chłonne w śródpiersiu przednim, zamostkowo, wielkości do 16x11mm, SUV max do 4,1  [Im fuz 104]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Poza powyższymi - węzły chłonne w śródpiersiu wielkości do 14x11mm.  Węzły chłonne międzypiersiowe i pachowe obustronnie wielkości do 13x9mm [strona prawa].  Brzuch i miednica: Wzmożona aktywność metaboliczna w topografii przydatków obustronnie, SUV max do 4,1 - w pierwszej kolejności czynnościowo. Utrzymuje się niewielka asymetria aktywności znacznika w nieposzerzonym UKM-ie nerki prawej i w prawym moczowodzie - zaburzenia odpływu moczu? do kontroli w wielofazowym badaniu TK jamy brzusznej i miednicy z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Wzmożona aktywność metaboliczna w brunatnej tkance tłuszczowej głowy i szyi, klatki piersiowej.  Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 3,5.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pobudzonych metabolicznie  węzłów chłonnch w śródpiersiu przednim - w porównaniu do poprzedniego badania PET/CT z dnia 4.01.2024r - częściowa regresja. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>5.3</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>05.11.2024</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>Ziarnica złośliwa. Niejasny obraz w KLP.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 64 min od podania 18F-FDG. Glikemia: 73mg%.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Wzmożony metabolizm FDG na tylnej ścianie nosogardła, SUV max 4,4 oraz w topografii struktur pierścienia Waldeyera SUV max do 8,4 -do kontroli laryngologicznej.  Asymetrycznie wzmożony metabolizm FDG w prawym fałdzie głośniowo-nalewkowym SUV max 4,4. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Wzmożony metabolizm FDG w topografii  - węzła chłonnego położonego za górną częścią rękojeści mostka na lewo od widocznych klipsów naczyniowych,   wielkości 13x10 mm SUV max 3,3 [Im fuz. 103] - w zmianie miękkotkankowej położonej zamostkowo poniżej opisywanego węzła chłonnego wielkości 18x8 mm SUV max 3,9 [Im fuz. 113]- masa resztkowa?grasica? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne przytchawicze dolne prawe wielkości do 14x16 mm.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne krezkowe: - w podbrzuszu po stronie prawej 11x19x19 mm SUV max 12,6  - w miednicy po stronie prawej wielkości do 16x13x31 mm SUV max do 9,3 [Im fuz. 221] Ogniskowo wzmożona aktywność metaboliczna w topografii endometrium SUV max 3,7 [Im fuz. 250]- w pierwszej kolejności o charakterze czynnościowym (OM 31.10.2024) Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Wzmożony metabolizm FDG w mięśniach przykręgosłupowych górnej części KLP, zwłaszcza po stronie lewej SUV max do 4,0- zmiany odczynowo-przeciążeniowe.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,3.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych po obu stronach przepony- w pierwszej kolejności progresja choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>12.6</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5 - znacznie zwiększony wychwyt lub nowe zmiany</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Progresja choroby. Klasyfikacja Lugano: Progressive Disease (PD) - progresja choroby. Deauville: 5 - znacznie zwiększony wychwyt lub nowe zmiany.</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>04.02.2025</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>Ziarnica złośliwa.  Kontrola. W opisie badania z listopada 2024 - stwierdzono progresję. Pacjentka przechodziła ostry stan zapalny przewodu pokarmowego.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 57 min od podania 18F-FDG. Glikemia: 83 mg%.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Wzmożony metabolizm FDG na tylnej ścianie nosogardła, SUV max 5,7 oraz w topografii struktur pierścienia Waldeyera SUV max do 6,5 -do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. W dolnej części szyi po stronie prawej, przytchawiczo-wydatniejsze zwapnienie? klips naczyniowy?  Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne w topografii: - węzła chłonnego położonego za górną częścią rękojeści mostka na lewo od widocznych klipsów naczyniowych,  wielkości 12x9 mm wg PET SUV max 3,0 [Im fuz. 100] - zmiany miękkotkankowej położonej zamostkowo poniżej opisywanego węzła chłonnego wielkości 20x9 mm SUV max 3,4 [Im fuz. 107] - masa resztkowa. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie węzeł chłonny okołoaortalny prawy poniżej naczyń nerkowych średnicy 8 mm wg PET SUV max 3,5 [Im fuz. 180] Pobudzone metabolicznie węzły chłonne krezkowe w podbrzuszu po stronie prawej  wielkości do 15x9mm SUV max do 2,9 Rozlanie wzmożony metabolizm FDG w topografii endometrium SUV max 7,5 [Im fuz. 247]- w pierwszej kolejności o charakterze czynnościowym (OM 01.02.2025). Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony. Drobne węzły chłonne biodrowe i pachwinowe obustronnie.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - aktywnego metabolicznie węzła chłonnego okołoaortalny prawego poniżej naczyń nerkowych - pobudzonych metabolicznie węzłów chłonnych po obu stronach przepony. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>7.5</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>27.10.2025</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>8</v>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>Ziarnica złośliwa. Badanie kontrolne.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 59 min od podania 18F-FDG. Glikemia: 88 mg%.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Wzmożony metabolizm FDG na tylnej ścianie nosogardła, SUV max 5,9 oraz w topografii zachyłka gruszkowatego po stronie prawej, SUV max 6,1- do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. W dolnej części szyi po stronie prawej, przytchawiczo-wydatniejsze zwapnienie? klips naczyniowy? Drobne węzły chłonne szyjne obustronnie.  Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne w topografii zmiany miękkotkankowej położonej zamostkowo wielkości 20x9mm SUV max 3,2 [Im fuz. 106] - masa resztkowa?. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Klipsy naczyniowe/znaczniki w śródpiersiu przednim, górnym. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2mm do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie obszar w miednicy po stronie lewej, wielkości 19x13mm wg PET, SUV max 6,8 [Im 241] - w jelitach? w przydatkach?- do oceny w badaniu MR miednicy z kontrastem dożylnym. Podobny, mniejszy, wielkości ok. 14x10mm wg PET, SUV max 5,7 - w miednicy po stronie prawej, w przyleganiu do trzonu macicy - do oceny j.w.  Rozlanie wzmożony metabolizm FDG w topografii jamy macicy i endometrium SUV max 4,2 [Im fuz. 251] - w pierwszej kolejności o charakterze czynnościowym. Rozlanie wzmożony metabolizm FDG w topografii dystalnej części pochwy, SUV max do 5,0 - zmiany zapalne? - do kontroli miejscowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony. Niewielka ilość płynu w jamie Douglasa po stronie prawej. Drobne węzły chłonne pachwinowe obustronnie.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo drobne wpuklenia blaszek granicznych trzonów kręgowych, zwłaszcza w odcinku szyjnym. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Zwiększony metabolizm FDG w tkance brunatnej szyi i KLP, nie da się jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród zwiększonego metabolizmu tkanki brunatnej- do kontroli.   Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,5.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego. Pobudzenie metaboliczne w topografii zmiany miękkotkankowej położonej zamostkowo - masa resztkowa?. Wskazane badanie MR miednicy -vide opis powyżej.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>6.8</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/ANNA TOKARCZYK.xlsx
+++ b/pacjenci/ANNA TOKARCZYK.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 77mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane przedziałów I - V obustronnie i nadobojczykowe obustronnie  wielkości do 35x25mm wg PET, SUV max do 6,2 (największy pakiet IM 83 strona lewa).  Poza tym fzjologiczny metabolizm FDG w obrębie głowy i szyi. Drobny polip lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane:  - podobojczykowe obustronnie, śródpiersiowe obustronnie, pachowe obustronnie, pojedyncze w strukturach mięśniowych ściany KLP wielkości do 21mm wg PET, SUV max do 5,8 - przytchawicze obustronnie, przy łuku aorty, przy tętnicy płucnej lewej, okna aortalno-płucnego wielkości do 23mm wg PET, SUV max do 5,6 - podostrogowe, obu wnęk wielkości do 38mm wg PET, SUV max do 7,6 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zgrubienie opłucnej płuca prawego grzbietowo. Drobne guzki w płacie górnym płuca prawego, w płacie górnym płuca lewego, w segm. 6L średnicy do 6mm.  Brzuch i miednica: Niejednoznaczny obszar pobudzenia metabolicznego przy torebce wątroby na poziomie segmentu 4 wielkości 11mm wg PET, SUV max 3,9- nie da się wykluczyć wychwytu pochodzącego z żebra 7. - celowa kontrola.  Drobny niejednoznaczny obszar pobudzenia metabolicznego wielkości 7mm wg PET, SUV max 3,1 dobocznie od żyły głównej dolnej [Im 181] węzeł chłonny krezkowy?- do oceny w badaniu TK z kontrastem dożylnym.  Obszar miękkotkankowy w miednicy po stronie lewej wielkości 27x25mm, SUV max 5,4 ze zwiększona aktywnością metaboliczną na obwodzie zmiany- zmiana ogniskowa przydatka lewego?- do oceny w USG- TV miednicy i konsultacji ginekologicznej. Zwiększona aktywność metaboliczna w macicy- związana z fazą cyklu?- do kontroli.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym do oceny z całością obrazu klinicznego ew. weryfikacji w trepanobiopsji.  Wartości referencyjne: MBPS SUVmax do 1,8 Prawy płat wątroby SUVmax do 2,6.</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane przedziałów I - V obustronnie i nadobojczykowe obustronnie  wielkości do 35x25mm wg PET, SUV max do 6,2 (największy pakiet IM 83 strona lewa).  Poza tym fzjologiczny metabolizm FDG w obrębie głowy i szyi. Drobny polip lewej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane:  - podobojczykowe obustronnie, śródpiersiowe obustronnie, pachowe obustronnie, pojedyncze w strukturach mięśniowych ściany KLP wielkości do 21mm wg PET, SUV max do 5,8 - przytchawicze obustronnie, przy łuku aorty, przy tętnicy płucnej lewej, okna aortalno-płucnego wielkości do 23mm wg PET, SUV max do 5,6 - podostrogowe, obu wnęk wielkości do 38mm wg PET, SUV max do 7,6 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zgrubienie opłucnej płuca prawego grzbietowo. Drobne guzki w płacie górnym płuca prawego, w płacie górnym płuca lewego, w segm. 6L średnicy do 6mm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Niejednoznaczny obszar pobudzenia metabolicznego przy torebce wątroby na poziomie segmentu 4 wielkości 11mm wg PET, SUV max 3,9- nie da się wykluczyć wychwytu pochodzącego z żebra 7. - celowa kontrola.  Drobny niejednoznaczny obszar pobudzenia metabolicznego wielkości 7mm wg PET, SUV max 3,1 dobocznie od żyły głównej dolnej [Im 181] węzeł chłonny krezkowy?- do oceny w badaniu TK z kontrastem dożylnym.  Obszar miękkotkankowy w miednicy po stronie lewej wielkości 27x25mm, SUV max 5,4 ze zwiększona aktywnością metaboliczną na obwodzie zmiany- zmiana ogniskowa przydatka lewego?- do oceny w USG- TV miednicy i konsultacji ginekologicznej. Zwiększona aktywność metaboliczna w macicy- związana z fazą cyklu?- do kontroli.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w układzie kostnym do oceny z całością obrazu klinicznego ew. weryfikacji w trepanobiopsji.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - aktywnych metabolicznie węzłow chłonnych na szyi i w KLP - niejednoznacznego obszaru przy torebce wątroby - nie da się wykluczyć wychwytu pochodzącego z żebra - celowa kontrola - niejednoznacznego obszaru w jamie brzusznej - węzeł chłonny krezkowy? - obszaru miękkotkankowego w miednicy po stronie lewej ze zwiększoną aktywnością metaboliczną na obwodzie zmiany- zmiana ogniskowa przydatka lewego?- do oceny w USG - TV i konsultacji ginekologicznej. Pobudzenie metaboliczne w układzie kostnym do oceny z całością obrazu klinicznego ew. weryfikacji w trepanobiopsji. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>7.6</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 57min od podania 18F-FDG. Glikemia: 68mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobny polip lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Bardzo drobne guzki w płacie górnym płuca prawego, w płacie górnym płuca lewego,  średnicy do 2-3mm. Węzły chłonne w śródpiersiu średnicy do 17mm.  Węzły chłonne pachowych obustronnie średnicy do 14mm.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym do oceny z całością obrazu klinicznego ew. weryfikacji w trepanobiopsji.  Wartości referencyjne: MBPS SUVmax do 2,5 Prawy płat wątroby SUVmax do 3,6,</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobny polip lewej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Bardzo drobne guzki w płacie górnym płuca prawego, w płacie górnym płuca lewego,  średnicy do 2-3mm. Węzły chłonne w śródpiersiu średnicy do 17mm.  Węzły chłonne pachowych obustronnie średnicy do 14mm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w układzie kostnym do oceny z całością obrazu klinicznego ew. weryfikacji w trepanobiopsji.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>3.6</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 56min od podania 18F-FDG. Glikemia: 76mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Drobne zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne w śródpiersiu wielkości do 17x15mm.  Węzły chłonne pachowe obustronnie wielkości do 15x11mm [strona prawa].  Brzuch i miednica: Wzmożona aktywność metaboliczna w topografii przydatków obustronnie, SUV max do 5,1 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwiększona ilość płynu w jamie Douglasa.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Wzmożona aktywność metaboliczna w brunatnej tkance tłuszczowej głowy i szyi, klatki piersiowej oraz nadbrzusza, SUV max do 11,6.  Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 2,9.</t>
+          <t>76</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Drobne zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne w śródpiersiu wielkości do 17x15mm.  Węzły chłonne pachowe obustronnie wielkości do 15x11mm [strona prawa].</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Wzmożona aktywność metaboliczna w topografii przydatków obustronnie, SUV max do 5,1 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwiększona ilość płynu w jamie Douglasa.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Nieco niejednorodny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Wzmożona aktywność metaboliczna w brunatnej tkance tłuszczowej głowy i szyi, klatki piersiowej oraz nadbrzusza, SUV max do 11,6.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>11.6</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 60min od podania 18F-FDG. Glikemia: 94mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Wzmożona aktywność metaboliczna w topografii mięśni jarzmowych obustronnie, SUVmax 4,8  [Im fuz 48] - w pierwszej kolejności czynnościowo. Wzmożona aktywność metaboliczna SUVmax do 4,7 w obrębie fałdów głosowych - czynnościowo. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Aktywne i pobudzone metabolicznie dość liczne, przylegające do siebie węzły chłonne w śródpiersiu przednim, zamostkowo, wielkości do 19x16mm, SUV max do 4,6  [Im fuz 109]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Poza powyższymi - węzły chłonne w śródpiersiu wielkości do 15x11mm.  Węzły chłonne międzypiersiowe i pachowe obustronnie wielkości do 15x11mm [strona prawa].  Brzuch i miednica: Wzmożona aktywność metaboliczna w topografii przydatków obustronnie, SUV max do 4,1 - w pierwszej kolejności czynnościowo. Utrzymuje się asymetria aktywności znacznika w nieposzerzonym UKM-ie nerki prawej i w prawym moczowodzie - zaburzenia odpływu moczu? do kontroli w wielofazowym badaniu TK jamy brzusznej i miednicy z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Wzmożona aktywność metaboliczna w brunatnej tkance tłuszczowej głowy i szyi, klatki piersiowej oraz nadbrzusza, SUV max do 14,5 - porównywalnie do poprzedniego badania PET z 13.07.2023r.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 3,2.</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Wzmożona aktywność metaboliczna w topografii mięśni jarzmowych obustronnie, SUVmax 4,8  [Im fuz 48] - w pierwszej kolejności czynnościowo. Wzmożona aktywność metaboliczna SUVmax do 4,7 w obrębie fałdów głosowych - czynnościowo. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Aktywne i pobudzone metabolicznie dość liczne, przylegające do siebie węzły chłonne w śródpiersiu przednim, zamostkowo, wielkości do 19x16mm, SUV max do 4,6  [Im fuz 109]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Poza powyższymi - węzły chłonne w śródpiersiu wielkości do 15x11mm.  Węzły chłonne międzypiersiowe i pachowe obustronnie wielkości do 15x11mm [strona prawa].</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Wzmożona aktywność metaboliczna w topografii przydatków obustronnie, SUV max do 4,1 - w pierwszej kolejności czynnościowo. Utrzymuje się asymetria aktywności znacznika w nieposzerzonym UKM-ie nerki prawej i w prawym moczowodzie - zaburzenia odpływu moczu? do kontroli w wielofazowym badaniu TK jamy brzusznej i miednicy z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Nieco niejednorodny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Wzmożona aktywność metaboliczna w brunatnej tkance tłuszczowej głowy i szyi, klatki piersiowej oraz nadbrzusza, SUV max do 14,5 - porównywalnie do poprzedniego badania PET z 13.07.2023r.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych i pobudzonych metabolicznie dość licznych, przylegających do siebie węzłów chłonnch w śródpiersiu przednim, zamostkowo - w porównaniu do poprzedniego badania PET/CT z dnia 13.07.2023r - progresja. Poza tym aktualny obraz badania PET porównywalny do poprzedniego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>14.5</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 57min od podania 18F-FDG. Glikemia: 83mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Pobudzenie metaboliczne na tylnej ścianie nosogardła, SUV max 5,3 -do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. Niewielkie przyścienne zgrubienia blony sluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Węzeł chłonny w śródpiersiu przednim, górnym po stronie lewej, wielkości 9mm, SUV max 3,7 [Im. Fuz. 93]. Aktywne metabolicznie przylegające do siebie węzły chłonne w śródpiersiu przednim, zamostkowo, wielkości do 16x11mm, SUV max do 4,1  [Im fuz 104]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Poza powyższymi - węzły chłonne w śródpiersiu wielkości do 14x11mm.  Węzły chłonne międzypiersiowe i pachowe obustronnie wielkości do 13x9mm [strona prawa].  Brzuch i miednica: Wzmożona aktywność metaboliczna w topografii przydatków obustronnie, SUV max do 4,1 - w pierwszej kolejności czynnościowo. Utrzymuje się niewielka asymetria aktywności znacznika w nieposzerzonym UKM-ie nerki prawej i w prawym moczowodzie - zaburzenia odpływu moczu? do kontroli w wielofazowym badaniu TK jamy brzusznej i miednicy z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Wzmożona aktywność metaboliczna w brunatnej tkance tłuszczowej głowy i szyi, klatki piersiowej.  Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 3,5.</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne na tylnej ścianie nosogardła, SUV max 5,3 -do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. Niewielkie przyścienne zgrubienia blony sluzowej w zachyłku zębodołowym prawej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Węzeł chłonny w śródpiersiu przednim, górnym po stronie lewej, wielkości 9mm, SUV max 3,7 [Im. Fuz. 93]. Aktywne metabolicznie przylegające do siebie węzły chłonne w śródpiersiu przednim, zamostkowo, wielkości do 16x11mm, SUV max do 4,1  [Im fuz 104]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Poza powyższymi - węzły chłonne w śródpiersiu wielkości do 14x11mm.  Węzły chłonne międzypiersiowe i pachowe obustronnie wielkości do 13x9mm [strona prawa].</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Wzmożona aktywność metaboliczna w topografii przydatków obustronnie, SUV max do 4,1 - w pierwszej kolejności czynnościowo. Utrzymuje się niewielka asymetria aktywności znacznika w nieposzerzonym UKM-ie nerki prawej i w prawym moczowodzie - zaburzenia odpływu moczu? do kontroli w wielofazowym badaniu TK jamy brzusznej i miednicy z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Wzmożona aktywność metaboliczna w brunatnej tkance tłuszczowej głowy i szyi, klatki piersiowej.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pobudzonych metabolicznie  węzłów chłonnch w śródpiersiu przednim - w porównaniu do poprzedniego badania PET/CT z dnia 4.01.2024r - częściowa regresja. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -634,20 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 64 min od podania 18F-FDG. Glikemia: 73mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG na tylnej ścianie nosogardła, SUV max 4,4 oraz w topografii struktur pierścienia Waldeyera SUV max do 8,4 -do kontroli laryngologicznej.  Asymetrycznie wzmożony metabolizm FDG w prawym fałdzie głośniowo-nalewkowym SUV max 4,4. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Wzmożony metabolizm FDG w topografii  - węzła chłonnego położonego za górną częścią rękojeści mostka na lewo od widocznych klipsów naczyniowych,   wielkości 13x10 mm SUV max 3,3 [Im fuz. 103] - w zmianie miękkotkankowej położonej zamostkowo poniżej opisywanego węzła chłonnego wielkości 18x8 mm SUV max 3,9 [Im fuz. 113]- masa resztkowa?grasica? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne przytchawicze dolne prawe wielkości do 14x16 mm.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne krezkowe: - w podbrzuszu po stronie prawej 11x19x19 mm SUV max 12,6  - w miednicy po stronie prawej wielkości do 16x13x31 mm SUV max do 9,3 [Im fuz. 221] Ogniskowo wzmożona aktywność metaboliczna w topografii endometrium SUV max 3,7 [Im fuz. 250]- w pierwszej kolejności o charakterze czynnościowym (OM 31.10.2024) Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Wzmożony metabolizm FDG w mięśniach przykręgosłupowych górnej części KLP, zwłaszcza po stronie lewej SUV max do 4,0- zmiany odczynowo-przeciążeniowe.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,3.</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG na tylnej ścianie nosogardła, SUV max 4,4 oraz w topografii struktur pierścienia Waldeyera SUV max do 8,4 -do kontroli laryngologicznej.  Asymetrycznie wzmożony metabolizm FDG w prawym fałdzie głośniowo-nalewkowym SUV max 4,4. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w topografii  - węzła chłonnego położonego za górną częścią rękojeści mostka na lewo od widocznych klipsów naczyniowych,   wielkości 13x10 mm SUV max 3,3 [Im fuz. 103] - w zmianie miękkotkankowej położonej zamostkowo poniżej opisywanego węzła chłonnego wielkości 18x8 mm SUV max 3,9 [Im fuz. 113]- masa resztkowa?grasica? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne przytchawicze dolne prawe wielkości do 14x16 mm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne krezkowe: - w podbrzuszu po stronie prawej 11x19x19 mm SUV max 12,6  - w miednicy po stronie prawej wielkości do 16x13x31 mm SUV max do 9,3 [Im fuz. 221] Ogniskowo wzmożona aktywność metaboliczna w topografii endometrium SUV max 3,7 [Im fuz. 250]- w pierwszej kolejności o charakterze czynnościowym (OM 31.10.2024) Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Wzmożony metabolizm FDG w mięśniach przykręgosłupowych górnej części KLP, zwłaszcza po stronie lewej SUV max do 4,0- zmiany odczynowo-przeciążeniowe.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych po obu stronach przepony- w pierwszej kolejności progresja choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="L7" t="n">
         <v>12.6</v>
       </c>
     </row>
@@ -667,20 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 57 min od podania 18F-FDG. Glikemia: 83 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG na tylnej ścianie nosogardła, SUV max 5,7 oraz w topografii struktur pierścienia Waldeyera SUV max do 6,5 -do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. W dolnej części szyi po stronie prawej, przytchawiczo-wydatniejsze zwapnienie? klips naczyniowy?  Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne w topografii: - węzła chłonnego położonego za górną częścią rękojeści mostka na lewo od widocznych klipsów naczyniowych,  wielkości 12x9 mm wg PET SUV max 3,0 [Im fuz. 100] - zmiany miękkotkankowej położonej zamostkowo poniżej opisywanego węzła chłonnego wielkości 20x9 mm SUV max 3,4 [Im fuz. 107] - masa resztkowa. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie węzeł chłonny okołoaortalny prawy poniżej naczyń nerkowych średnicy 8 mm wg PET SUV max 3,5 [Im fuz. 180] Pobudzone metabolicznie węzły chłonne krezkowe w podbrzuszu po stronie prawej  wielkości do 15x9mm SUV max do 2,9 Rozlanie wzmożony metabolizm FDG w topografii endometrium SUV max 7,5 [Im fuz. 247]- w pierwszej kolejności o charakterze czynnościowym (OM 01.02.2025). Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony. Drobne węzły chłonne biodrowe i pachwinowe obustronnie.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG na tylnej ścianie nosogardła, SUV max 5,7 oraz w topografii struktur pierścienia Waldeyera SUV max do 6,5 -do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. W dolnej części szyi po stronie prawej, przytchawiczo-wydatniejsze zwapnienie? klips naczyniowy?</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w topografii: - węzła chłonnego położonego za górną częścią rękojeści mostka na lewo od widocznych klipsów naczyniowych,  wielkości 12x9 mm wg PET SUV max 3,0 [Im fuz. 100] - zmiany miękkotkankowej położonej zamostkowo poniżej opisywanego węzła chłonnego wielkości 20x9 mm SUV max 3,4 [Im fuz. 107] - masa resztkowa. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2 do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny okołoaortalny prawy poniżej naczyń nerkowych średnicy 8 mm wg PET SUV max 3,5 [Im fuz. 180] Pobudzone metabolicznie węzły chłonne krezkowe w podbrzuszu po stronie prawej  wielkości do 15x9mm SUV max do 2,9 Rozlanie wzmożony metabolizm FDG w topografii endometrium SUV max 7,5 [Im fuz. 247]- w pierwszej kolejności o charakterze czynnościowym (OM 01.02.2025). Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony. Drobne węzły chłonne biodrowe i pachwinowe obustronnie.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - aktywnego metabolicznie węzła chłonnego okołoaortalny prawego poniżej naczyń nerkowych - pobudzonych metabolicznie węzłów chłonnych po obu stronach przepony. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="L8" t="n">
         <v>7.5</v>
       </c>
     </row>
@@ -700,20 +900,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 59 min od podania 18F-FDG. Glikemia: 88 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG na tylnej ścianie nosogardła, SUV max 5,9 oraz w topografii zachyłka gruszkowatego po stronie prawej, SUV max 6,1- do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. W dolnej części szyi po stronie prawej, przytchawiczo-wydatniejsze zwapnienie? klips naczyniowy? Drobne węzły chłonne szyjne obustronnie.  Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne w topografii zmiany miękkotkankowej położonej zamostkowo wielkości 20x9mm SUV max 3,2 [Im fuz. 106] - masa resztkowa?. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Klipsy naczyniowe/znaczniki w śródpiersiu przednim, górnym. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2mm do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie obszar w miednicy po stronie lewej, wielkości 19x13mm wg PET, SUV max 6,8 [Im 241] - w jelitach? w przydatkach?- do oceny w badaniu MR miednicy z kontrastem dożylnym. Podobny, mniejszy, wielkości ok. 14x10mm wg PET, SUV max 5,7 - w miednicy po stronie prawej, w przyleganiu do trzonu macicy - do oceny j.w.  Rozlanie wzmożony metabolizm FDG w topografii jamy macicy i endometrium SUV max 4,2 [Im fuz. 251] - w pierwszej kolejności o charakterze czynnościowym. Rozlanie wzmożony metabolizm FDG w topografii dystalnej części pochwy, SUV max do 5,0 - zmiany zapalne? - do kontroli miejscowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony. Niewielka ilość płynu w jamie Douglasa po stronie prawej. Drobne węzły chłonne pachwinowe obustronnie.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo drobne wpuklenia blaszek granicznych trzonów kręgowych, zwłaszcza w odcinku szyjnym. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Zwiększony metabolizm FDG w tkance brunatnej szyi i KLP, nie da się jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród zwiększonego metabolizmu tkanki brunatnej- do kontroli.   Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,5.</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG na tylnej ścianie nosogardła, SUV max 5,9 oraz w topografii zachyłka gruszkowatego po stronie prawej, SUV max 6,1- do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. W dolnej części szyi po stronie prawej, przytchawiczo-wydatniejsze zwapnienie? klips naczyniowy? Drobne węzły chłonne szyjne obustronnie.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w topografii zmiany miękkotkankowej położonej zamostkowo wielkości 20x9mm SUV max 3,2 [Im fuz. 106] - masa resztkowa?. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Klipsy naczyniowe/znaczniki w śródpiersiu przednim, górnym. Pojedyncze, drobne guzki w płacie górnym płuca prawego i lewego,  średnicy 2mm do 3mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w miednicy po stronie lewej, wielkości 19x13mm wg PET, SUV max 6,8 [Im 241] - w jelitach? w przydatkach?- do oceny w badaniu MR miednicy z kontrastem dożylnym. Podobny, mniejszy, wielkości ok. 14x10mm wg PET, SUV max 5,7 - w miednicy po stronie prawej, w przyleganiu do trzonu macicy - do oceny j.w.  Rozlanie wzmożony metabolizm FDG w topografii jamy macicy i endometrium SUV max 4,2 [Im fuz. 251] - w pierwszej kolejności o charakterze czynnościowym. Rozlanie wzmożony metabolizm FDG w topografii dystalnej części pochwy, SUV max do 5,0 - zmiany zapalne? - do kontroli miejscowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wydłużony lewy płat wątroby, sięga poza przednio-lewoboczny obrys śledziony. Niewielka ilość płynu w jamie Douglasa po stronie prawej. Drobne węzły chłonne pachwinowe obustronnie.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Drobne zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo drobne wpuklenia blaszek granicznych trzonów kręgowych, zwłaszcza w odcinku szyjnym. Niewielka esowata skolioza kręgosłupa piersiowego-lewowypukła w części górnej i prawowypukła w części środkowo-dolnej. Na poziomie L4/L5 po stronie prawej spondyloliza - aktualnie bez spondylolistezy. Os sacrum arcuatum. Drobne wyspy kostne w głowie prawej kości udowej oraz w panewce prawego stawu udowego.  Inne: Zwiększony metabolizm FDG w tkance brunatnej szyi i KLP, nie da się jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród zwiększonego metabolizmu tkanki brunatnej- do kontroli.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego. Pobudzenie metaboliczne w topografii zmiany miękkotkankowej położonej zamostkowo - masa resztkowa?. Wskazane badanie MR miednicy -vide opis powyżej.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="L9" t="n">
         <v>6.8</v>
       </c>
     </row>
